--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1548,6 +1548,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -8781,7 +8785,7 @@
         <v>486</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>487</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8796,7 +8800,7 @@
         <v>477</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8804,10 +8808,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8833,10 +8837,10 @@
         <v>483</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8887,7 +8891,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8899,7 +8903,7 @@
         <v>486</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>487</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8914,7 +8918,7 @@
         <v>477</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8922,10 +8926,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8951,10 +8955,10 @@
         <v>243</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8984,10 +8988,10 @@
         <v>259</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9005,7 +9009,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9032,7 +9036,7 @@
         <v>477</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9040,10 +9044,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9069,16 +9073,16 @@
         <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9106,10 +9110,10 @@
         <v>248</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9127,7 +9131,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9148,10 +9152,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>416</v>
@@ -9162,10 +9166,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9191,16 +9195,16 @@
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9228,10 +9232,10 @@
         <v>430</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9249,7 +9253,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9270,10 +9274,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>416</v>
@@ -9284,10 +9288,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9310,17 +9314,17 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9369,7 +9373,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9396,7 +9400,7 @@
         <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9404,10 +9408,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9430,13 +9434,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9487,7 +9491,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9514,7 +9518,7 @@
         <v>477</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9522,10 +9526,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9548,16 +9552,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9607,7 +9611,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9631,7 +9635,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>209</v>
@@ -9642,10 +9646,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9668,16 +9672,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9727,7 +9731,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9751,10 +9755,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -9762,10 +9766,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9791,16 +9795,16 @@
         <v>186</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9849,7 +9853,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9873,10 +9877,10 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -9884,10 +9888,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10002,10 +10006,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10122,10 +10126,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10244,10 +10248,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10273,13 +10277,13 @@
         <v>243</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>258</v>
@@ -10310,10 +10314,10 @@
         <v>430</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10331,7 +10335,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10352,7 +10356,7 @@
         <v>263</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>265</v>
@@ -10366,10 +10370,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10392,16 +10396,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M69" t="s" s="2">
         <v>325</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>327</v>
@@ -10453,7 +10457,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10474,7 +10478,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>332</v>
@@ -10488,10 +10492,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10517,13 +10521,13 @@
         <v>243</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>401</v>
@@ -10575,7 +10579,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10610,10 +10614,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10697,7 +10701,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10732,10 +10736,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10761,10 +10765,10 @@
         <v>83</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>474</v>
@@ -10819,7 +10823,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
